--- a/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_3/CF_M06_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,55 +481,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WebSocket</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Via sockets es poden rebre els logs en temps real.</t>
+          <t>Communication protocol used for real-time logs and preview.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>38, 70, 79</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_03, AU_02</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>presentation layer, waapiti server</t>
-        </is>
-      </c>
+          <t>AU_19, AU_20</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>CF_M06_AU29</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>This functionality connects via socket [25] with the server and displays</t>
+          <t>This will interact with the Waapiti API using HTTP requests.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -540,42 +544,90 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Per poder implementar aquesta funcionalitat és necessari utilitzar un servei de missatgeria per cada plataforma: Firebase Cloud Messaging (FCM) per dispositius Android i Apple Push Notification Service (APNS) per dispositius iOS. [...] AWS SNS és un servei administrat el qual ofereix el lliurament de missatges dels publicadors als subscriptors.</t>
+          <t>Via sockets, logs can be received in real time.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>91,92</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_02, AU_12, AU_13, AU_14</t>
+          <t>AU_03, AU_02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>waapiti server, aws sns, firebase cloud messaging, apple push notification service</t>
+          <t>presentation layer, waapiti server</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M06_AU22</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>AWS SNS</t>
-        </is>
-      </c>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>In the end it was decided to use AWS SNS due to the cost compared to Expo Push API. In addition, AWS SNS is more scalable and can be used by other services.</t>
+          <t>This functionality connects via socket [25] with the server and displays</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7326</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The application uses Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices to receive push notifications.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_03, AU_12, AU_13</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>presentation layer, firebase cloud messaging, apple push notification service</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CF_M06_AU20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8037</v>
       </c>
     </row>
   </sheetData>
